--- a/data/trans_bre/P2A_enfcro_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,5; 7,86</t>
+          <t>-15,88; 7,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 23,12</t>
+          <t>-5,22; 21,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 14,93</t>
+          <t>-10,53; 15,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 2,39</t>
+          <t>-3,13; 2,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-41,32; 28,91</t>
+          <t>-41,17; 28,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 86,95</t>
+          <t>-13,13; 75,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-27,71; 46,77</t>
+          <t>-24,29; 46,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 2,48</t>
+          <t>-3,14; 2,2</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 12,59</t>
+          <t>-17,51; 11,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,83; 11,86</t>
+          <t>-16,47; 11,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,47; 5,15</t>
+          <t>-18,14; 5,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 2,79</t>
+          <t>-5,46; 2,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,19; 33,19</t>
+          <t>-32,35; 27,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,82; 31,08</t>
+          <t>-32,98; 30,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,01; 14,6</t>
+          <t>-39,8; 16,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 2,86</t>
+          <t>-5,52; 2,55</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,85; 8,21</t>
+          <t>-17,47; 7,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 21,22</t>
+          <t>-7,33; 19,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,19; 15,04</t>
+          <t>-14,09; 15,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 3,77</t>
+          <t>-12,15; 3,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-42,49; 33,62</t>
+          <t>-43,77; 27,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 67,14</t>
+          <t>-15,38; 62,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-32,2; 51,21</t>
+          <t>-32,88; 53,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 3,93</t>
+          <t>-12,29; 3,94</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,41; 7,56</t>
+          <t>-11,42; 6,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,46; 5,99</t>
+          <t>-14,07; 4,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 18,12</t>
+          <t>1,71; 18,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 6,17</t>
+          <t>-0,57; 6,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,01; 20,23</t>
+          <t>-24,77; 17,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,53; 11,92</t>
+          <t>-24,28; 8,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 60,39</t>
+          <t>4,3; 60,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 6,73</t>
+          <t>-0,58; 7,09</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 10,34</t>
+          <t>-15,68; 9,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-24,5; -0,22</t>
+          <t>-24,15; -0,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,54; 4,46</t>
+          <t>-18,89; 4,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 6,02</t>
+          <t>-6,69; 6,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,47; 26,56</t>
+          <t>-30,68; 24,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-39,07; 0,54</t>
+          <t>-39,28; -0,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-33,32; 9,32</t>
+          <t>-31,39; 9,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 6,98</t>
+          <t>-7,24; 7,29</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,19; 9,52</t>
+          <t>-17,9; 8,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 19,54</t>
+          <t>-11,53; 18,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 17,52</t>
+          <t>-11,94; 17,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 9,49</t>
+          <t>-7,82; 8,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-28,85; 20,25</t>
+          <t>-29,45; 17,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 44,98</t>
+          <t>-20,6; 42,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-24,17; 52,31</t>
+          <t>-24,11; 50,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 10,95</t>
+          <t>-8,09; 9,34</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 2,03</t>
+          <t>-8,28; 1,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 3,49</t>
+          <t>-6,59; 3,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 6,43</t>
+          <t>-3,38; 6,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,58</t>
+          <t>-1,4; 2,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-17,45; 4,93</t>
+          <t>-18,45; 4,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 7,52</t>
+          <t>-12,86; 7,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 16,97</t>
+          <t>-7,65; 16,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 2,76</t>
+          <t>-1,46; 3,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_enfcro_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,88; 7,86</t>
+          <t>-16,19; 8,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 21,11</t>
+          <t>-4,4; 23,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 15,4</t>
+          <t>-11,79; 14,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 2,14</t>
+          <t>-3,05; 2,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-41,17; 28,72</t>
+          <t>-39,51; 31,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 75,78</t>
+          <t>-10,74; 81,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-24,29; 46,87</t>
+          <t>-26,54; 44,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 2,2</t>
+          <t>-3,08; 2,38</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 11,23</t>
+          <t>-15,69; 12,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,47; 11,72</t>
+          <t>-17,47; 11,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,14; 5,72</t>
+          <t>-18,08; 5,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 2,51</t>
+          <t>-5,06; 2,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,35; 27,65</t>
+          <t>-29,9; 31,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,98; 30,51</t>
+          <t>-32,54; 31,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,8; 16,15</t>
+          <t>-38,14; 15,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 2,55</t>
+          <t>-5,07; 2,23</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,47; 7,99</t>
+          <t>-15,68; 10,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 19,99</t>
+          <t>-6,85; 20,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 15,14</t>
+          <t>-14,69; 14,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 3,75</t>
+          <t>-13,11; 3,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-43,77; 27,08</t>
+          <t>-41,16; 34,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,38; 62,9</t>
+          <t>-14,58; 63,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-32,88; 53,23</t>
+          <t>-34,39; 50,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 3,94</t>
+          <t>-13,51; 3,86</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 6,4</t>
+          <t>-11,54; 6,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,07; 4,3</t>
+          <t>-14,33; 4,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 18,33</t>
+          <t>1,59; 17,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 6,38</t>
+          <t>-0,63; 6,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,77; 17,76</t>
+          <t>-24,83; 18,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 8,6</t>
+          <t>-25,57; 8,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,3; 60,08</t>
+          <t>4,11; 57,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 7,09</t>
+          <t>-0,65; 6,99</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 9,87</t>
+          <t>-15,53; 10,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-24,15; -0,04</t>
+          <t>-24,92; 0,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,89; 4,4</t>
+          <t>-17,97; 5,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 6,27</t>
+          <t>-6,44; 7,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-30,68; 24,21</t>
+          <t>-29,14; 25,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-39,28; -0,25</t>
+          <t>-39,44; 0,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,39; 9,87</t>
+          <t>-30,81; 11,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 7,29</t>
+          <t>-6,93; 8,6</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,9; 8,32</t>
+          <t>-18,1; 8,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 18,16</t>
+          <t>-8,91; 18,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 17,43</t>
+          <t>-11,61; 18,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 8,05</t>
+          <t>-7,25; 8,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,45; 17,32</t>
+          <t>-30,02; 17,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,6; 42,25</t>
+          <t>-16,37; 42,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-24,11; 50,25</t>
+          <t>-24,08; 50,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 9,34</t>
+          <t>-7,57; 9,69</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 1,92</t>
+          <t>-8,07; 1,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 3,38</t>
+          <t>-6,63; 3,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 6,25</t>
+          <t>-3,54; 6,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 2,82</t>
+          <t>-1,54; 2,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-18,45; 4,66</t>
+          <t>-17,76; 4,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 7,58</t>
+          <t>-12,99; 8,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 16,46</t>
+          <t>-8,24; 15,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 3,05</t>
+          <t>-1,62; 2,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_enfcro_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,06</t>
+          <t>-0,19</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-0,06%</t>
+          <t>-0,19%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 8,54</t>
+          <t>-16,5; 7,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 23,01</t>
+          <t>-5,28; 23,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,79; 14,8</t>
+          <t>-12,27; 14,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 2,31</t>
+          <t>-3,24; 2,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-39,51; 31,78</t>
+          <t>-41,32; 28,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 81,85</t>
+          <t>-12,64; 86,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-26,54; 44,5</t>
+          <t>-27,71; 46,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 2,38</t>
+          <t>-3,29; 2,34</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,96</t>
+          <t>-1,09</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-0,98%</t>
+          <t>-1,11%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,69; 12,66</t>
+          <t>-15,34; 12,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,47; 11,81</t>
+          <t>-15,83; 11,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 5,48</t>
+          <t>-18,47; 5,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 2,17</t>
+          <t>-4,81; 2,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,9; 31,21</t>
+          <t>-29,19; 33,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,54; 31,25</t>
+          <t>-30,82; 31,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,14; 15,96</t>
+          <t>-39,01; 14,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 2,23</t>
+          <t>-4,88; 2,96</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,57</t>
+          <t>-3,29</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-3,69%</t>
+          <t>-3,4%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 10,01</t>
+          <t>-16,85; 8,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 20,34</t>
+          <t>-7,52; 21,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,69; 14,07</t>
+          <t>-14,19; 15,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 3,64</t>
+          <t>-12,14; 3,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-41,16; 34,99</t>
+          <t>-42,49; 33,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 63,1</t>
+          <t>-15,6; 67,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-34,39; 50,38</t>
+          <t>-32,2; 51,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 3,86</t>
+          <t>-12,16; 4,09</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,57</t>
+          <t>2,4</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 6,89</t>
+          <t>-11,41; 7,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 4,21</t>
+          <t>-13,46; 5,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 17,42</t>
+          <t>0,81; 18,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 6,37</t>
+          <t>-0,98; 6,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,83; 18,75</t>
+          <t>-24,01; 20,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,57; 8,36</t>
+          <t>-23,53; 11,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,11; 57,28</t>
+          <t>2,09; 60,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 6,99</t>
+          <t>-1,01; 6,63</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>-0,08</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-0,19%</t>
+          <t>-0,09%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,53; 10,33</t>
+          <t>-15,05; 10,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-24,92; 0,23</t>
+          <t>-24,5; -0,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 5,02</t>
+          <t>-19,54; 4,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 7,18</t>
+          <t>-6,84; 6,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-29,14; 25,51</t>
+          <t>-28,47; 26,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-39,44; 0,78</t>
+          <t>-39,07; 0,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-30,81; 11,08</t>
+          <t>-33,32; 9,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 8,6</t>
+          <t>-7,29; 7,07</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>-0,45</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>-0,48%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-18,1; 8,5</t>
+          <t>-17,19; 9,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 18,18</t>
+          <t>-9,46; 19,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 18,12</t>
+          <t>-11,99; 17,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 8,42</t>
+          <t>-7,46; 9,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,02; 17,2</t>
+          <t>-28,85; 20,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 42,24</t>
+          <t>-17,58; 44,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-24,08; 50,89</t>
+          <t>-24,17; 52,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 9,69</t>
+          <t>-7,81; 10,33</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,28</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 1,96</t>
+          <t>-7,82; 2,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 3,89</t>
+          <t>-6,78; 3,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 6,01</t>
+          <t>-3,16; 6,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 2,7</t>
+          <t>-1,82; 2,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-17,76; 4,74</t>
+          <t>-17,45; 4,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 8,53</t>
+          <t>-13,48; 7,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 15,2</t>
+          <t>-7,48; 16,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 2,87</t>
+          <t>-1,89; 2,62</t>
         </is>
       </c>
     </row>
